--- a/static/data/exports/Retro_GA_AE_2022.xlsx
+++ b/static/data/exports/Retro_GA_AE_2022.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,6 +576,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>40</v>
+      </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
@@ -638,6 +651,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>57</v>
+      </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
@@ -700,6 +726,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>65</v>
+      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -762,6 +801,19 @@
           <t>GFP</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>49</v>
+      </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
@@ -824,6 +876,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>32</v>
+      </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
@@ -886,6 +951,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>45</v>
+      </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
@@ -949,7 +1027,7 @@
         </is>
       </c>
       <c r="Q8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>45</v>
@@ -1010,6 +1088,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>53</v>
+      </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
@@ -1072,6 +1163,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>31</v>
+      </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
@@ -1134,6 +1238,19 @@
           <t>SBBGP</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>45</v>
+      </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
@@ -1196,6 +1313,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>47</v>
+      </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
@@ -1258,6 +1388,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>57</v>
+      </c>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
@@ -1320,6 +1463,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>28</v>
+      </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
@@ -1382,6 +1538,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>36</v>
+      </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
@@ -1444,6 +1613,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>46</v>
+      </c>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
@@ -1507,7 +1689,7 @@
         </is>
       </c>
       <c r="Q17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>45</v>
@@ -1568,6 +1750,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>51</v>
+      </c>
       <c r="Q18" t="b">
         <v>0</v>
       </c>
@@ -1630,6 +1825,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>52</v>
+      </c>
       <c r="Q19" t="b">
         <v>0</v>
       </c>
@@ -1692,6 +1900,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>60</v>
+      </c>
       <c r="Q20" t="b">
         <v>0</v>
       </c>
@@ -1754,6 +1975,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>47</v>
+      </c>
       <c r="Q21" t="b">
         <v>0</v>
       </c>
@@ -1816,6 +2050,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>50</v>
+      </c>
       <c r="Q22" t="b">
         <v>0</v>
       </c>
@@ -1878,8 +2125,21 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>56</v>
+      </c>
       <c r="Q23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>45</v>
@@ -1940,6 +2200,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>58</v>
+      </c>
       <c r="Q24" t="b">
         <v>1</v>
       </c>
@@ -2002,6 +2275,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>47</v>
+      </c>
       <c r="Q25" t="b">
         <v>0</v>
       </c>
@@ -2064,6 +2350,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>31</v>
+      </c>
       <c r="Q26" t="b">
         <v>0</v>
       </c>
@@ -2127,7 +2426,7 @@
         </is>
       </c>
       <c r="Q27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>45</v>
@@ -2188,6 +2487,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>61</v>
+      </c>
       <c r="Q28" t="b">
         <v>0</v>
       </c>
@@ -2250,6 +2562,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>45</v>
+      </c>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
@@ -2312,6 +2637,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>37</v>
+      </c>
       <c r="Q30" t="b">
         <v>0</v>
       </c>
@@ -2374,6 +2712,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>44</v>
+      </c>
       <c r="Q31" t="b">
         <v>0</v>
       </c>
@@ -2436,6 +2787,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>59</v>
+      </c>
       <c r="Q32" t="b">
         <v>0</v>
       </c>
@@ -2499,7 +2863,7 @@
         </is>
       </c>
       <c r="Q33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>45</v>
@@ -2560,6 +2924,19 @@
           <t>GSB</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>38</v>
+      </c>
       <c r="Q34" t="b">
         <v>0</v>
       </c>
@@ -2622,6 +2999,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>38</v>
+      </c>
       <c r="Q35" t="b">
         <v>0</v>
       </c>
@@ -2684,6 +3074,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>33</v>
+      </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
@@ -2746,6 +3149,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>64</v>
+      </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
@@ -2808,6 +3224,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>50</v>
+      </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
@@ -2870,6 +3299,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>42</v>
+      </c>
       <c r="Q39" t="b">
         <v>0</v>
       </c>
@@ -2932,6 +3374,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>27</v>
+      </c>
       <c r="Q40" t="b">
         <v>0</v>
       </c>
@@ -2995,7 +3450,7 @@
         </is>
       </c>
       <c r="Q41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>45</v>
@@ -3056,6 +3511,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>43</v>
+      </c>
       <c r="Q42" t="b">
         <v>0</v>
       </c>
@@ -3118,6 +3586,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>39</v>
+      </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
@@ -3180,6 +3661,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>59</v>
+      </c>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
@@ -3242,6 +3736,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>44</v>
+      </c>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
@@ -3304,8 +3811,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>65</v>
+      </c>
       <c r="Q46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>45</v>
@@ -3366,6 +3886,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>28</v>
+      </c>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
@@ -3428,8 +3961,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>50</v>
+      </c>
       <c r="Q48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>45</v>
@@ -3490,6 +4036,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>40</v>
+      </c>
       <c r="Q49" t="b">
         <v>0</v>
       </c>
@@ -3552,6 +4111,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>57</v>
+      </c>
       <c r="Q50" t="b">
         <v>0</v>
       </c>
@@ -3614,6 +4186,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>59</v>
+      </c>
       <c r="Q51" t="b">
         <v>0</v>
       </c>
@@ -3676,6 +4261,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>52</v>
+      </c>
       <c r="Q52" t="b">
         <v>0</v>
       </c>
@@ -3739,7 +4337,7 @@
         </is>
       </c>
       <c r="Q53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>45</v>
@@ -3800,6 +4398,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>37</v>
+      </c>
       <c r="Q54" t="b">
         <v>0</v>
       </c>
@@ -3862,6 +4473,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>43</v>
+      </c>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
@@ -3924,6 +4548,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>53</v>
+      </c>
       <c r="Q56" t="b">
         <v>0</v>
       </c>
@@ -3986,6 +4623,19 @@
           <t>SBBGP</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>39</v>
+      </c>
       <c r="Q57" t="b">
         <v>0</v>
       </c>
@@ -4048,6 +4698,19 @@
           <t>JMBP</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>65</v>
+      </c>
       <c r="Q58" t="b">
         <v>0</v>
       </c>
@@ -4110,6 +4773,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>43</v>
+      </c>
       <c r="Q59" t="b">
         <v>0</v>
       </c>
@@ -4172,6 +4848,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>47</v>
+      </c>
       <c r="Q60" t="b">
         <v>0</v>
       </c>
@@ -4234,6 +4923,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>36</v>
+      </c>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
@@ -4296,6 +4998,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>45</v>
+      </c>
       <c r="Q62" t="b">
         <v>0</v>
       </c>
@@ -4358,6 +5073,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>49</v>
+      </c>
       <c r="Q63" t="b">
         <v>0</v>
       </c>
@@ -4420,6 +5148,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>53</v>
+      </c>
       <c r="Q64" t="b">
         <v>0</v>
       </c>
@@ -4483,7 +5224,7 @@
         </is>
       </c>
       <c r="Q65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>45</v>
@@ -4544,6 +5285,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>45</v>
+      </c>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
@@ -4606,6 +5360,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>61</v>
+      </c>
       <c r="Q67" t="b">
         <v>0</v>
       </c>
@@ -4668,6 +5435,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>52</v>
+      </c>
       <c r="Q68" t="b">
         <v>0</v>
       </c>
@@ -4730,6 +5510,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>33</v>
+      </c>
       <c r="Q69" t="b">
         <v>0</v>
       </c>
@@ -4792,6 +5585,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>58</v>
+      </c>
       <c r="Q70" t="b">
         <v>0</v>
       </c>
@@ -4854,6 +5660,19 @@
           <t>GSB</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>43</v>
+      </c>
       <c r="Q71" t="b">
         <v>0</v>
       </c>
@@ -4916,6 +5735,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>54</v>
+      </c>
       <c r="Q72" t="b">
         <v>0</v>
       </c>
@@ -4979,7 +5811,7 @@
         </is>
       </c>
       <c r="Q73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>45</v>
@@ -5040,6 +5872,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>47</v>
+      </c>
       <c r="Q74" t="b">
         <v>0</v>
       </c>
@@ -5102,6 +5947,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>52</v>
+      </c>
       <c r="Q75" t="b">
         <v>0</v>
       </c>
@@ -5164,6 +6022,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>44</v>
+      </c>
       <c r="Q76" t="b">
         <v>0</v>
       </c>
@@ -5226,6 +6097,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>48</v>
+      </c>
       <c r="Q77" t="b">
         <v>0</v>
       </c>
@@ -5289,7 +6173,7 @@
         </is>
       </c>
       <c r="Q78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>45</v>
@@ -5350,6 +6234,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>42</v>
+      </c>
       <c r="Q79" t="b">
         <v>0</v>
       </c>
@@ -5412,6 +6309,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>55</v>
+      </c>
       <c r="Q80" t="b">
         <v>0</v>
       </c>
@@ -5474,6 +6384,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>59</v>
+      </c>
       <c r="Q81" t="b">
         <v>0</v>
       </c>
@@ -5536,6 +6459,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>50</v>
+      </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
@@ -5598,6 +6534,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>43</v>
+      </c>
       <c r="Q83" t="b">
         <v>0</v>
       </c>
@@ -5660,6 +6609,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>44</v>
+      </c>
       <c r="Q84" t="b">
         <v>0</v>
       </c>
@@ -5723,7 +6685,7 @@
         </is>
       </c>
       <c r="Q85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
         <v>45</v>
@@ -5784,6 +6746,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>42</v>
+      </c>
       <c r="Q86" t="b">
         <v>0</v>
       </c>
@@ -5846,6 +6821,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>59</v>
+      </c>
       <c r="Q87" t="b">
         <v>0</v>
       </c>
@@ -5908,6 +6896,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>41</v>
+      </c>
       <c r="Q88" t="b">
         <v>0</v>
       </c>
@@ -5970,6 +6971,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>59</v>
+      </c>
       <c r="Q89" t="b">
         <v>0</v>
       </c>
@@ -6032,6 +7046,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>45</v>
+      </c>
       <c r="Q90" t="b">
         <v>0</v>
       </c>
@@ -6094,6 +7121,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>50</v>
+      </c>
       <c r="Q91" t="b">
         <v>0</v>
       </c>
@@ -6157,7 +7197,7 @@
         </is>
       </c>
       <c r="Q92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>45</v>
@@ -6218,6 +7258,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>47</v>
+      </c>
       <c r="Q93" t="b">
         <v>0</v>
       </c>
@@ -6280,6 +7333,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>46</v>
+      </c>
       <c r="Q94" t="b">
         <v>0</v>
       </c>
@@ -6342,6 +7408,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>51</v>
+      </c>
       <c r="Q95" t="b">
         <v>0</v>
       </c>
@@ -6404,6 +7483,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>66</v>
+      </c>
       <c r="Q96" t="b">
         <v>0</v>
       </c>
@@ -6466,8 +7558,21 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>39</v>
+      </c>
       <c r="Q97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
         <v>45</v>
@@ -6528,6 +7633,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>34</v>
+      </c>
       <c r="Q98" t="b">
         <v>0</v>
       </c>
@@ -6591,7 +7709,7 @@
         </is>
       </c>
       <c r="Q99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>45</v>
@@ -6652,6 +7770,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>47</v>
+      </c>
       <c r="Q100" t="b">
         <v>0</v>
       </c>
@@ -6714,6 +7845,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>30</v>
+      </c>
       <c r="Q101" t="b">
         <v>0</v>
       </c>
@@ -6776,6 +7920,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>35</v>
+      </c>
       <c r="Q102" t="b">
         <v>0</v>
       </c>
@@ -6838,6 +7995,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>58</v>
+      </c>
       <c r="Q103" t="b">
         <v>0</v>
       </c>
@@ -6900,6 +8070,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>55</v>
+      </c>
       <c r="Q104" t="b">
         <v>0</v>
       </c>
@@ -6962,6 +8145,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>56</v>
+      </c>
       <c r="Q105" t="b">
         <v>0</v>
       </c>
@@ -7024,6 +8220,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>45</v>
+      </c>
       <c r="Q106" t="b">
         <v>0</v>
       </c>
@@ -7086,6 +8295,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>33</v>
+      </c>
       <c r="Q107" t="b">
         <v>0</v>
       </c>
@@ -7148,6 +8370,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>60</v>
+      </c>
       <c r="Q108" t="b">
         <v>0</v>
       </c>
@@ -7211,7 +8446,7 @@
         </is>
       </c>
       <c r="Q109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>45</v>
@@ -7272,6 +8507,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>28</v>
+      </c>
       <c r="Q110" t="b">
         <v>0</v>
       </c>
@@ -7334,6 +8582,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>53</v>
+      </c>
       <c r="Q111" t="b">
         <v>0</v>
       </c>
@@ -7396,6 +8657,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>56</v>
+      </c>
       <c r="Q112" t="b">
         <v>0</v>
       </c>
@@ -7458,6 +8732,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>52</v>
+      </c>
       <c r="Q113" t="b">
         <v>0</v>
       </c>
@@ -7520,6 +8807,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>55</v>
+      </c>
       <c r="Q114" t="b">
         <v>0</v>
       </c>
@@ -7582,6 +8882,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>36</v>
+      </c>
       <c r="Q115" t="b">
         <v>0</v>
       </c>
@@ -7645,7 +8958,7 @@
         </is>
       </c>
       <c r="Q116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>45</v>
@@ -7706,6 +9019,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>32</v>
+      </c>
       <c r="Q117" t="b">
         <v>0</v>
       </c>
@@ -7768,6 +9094,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>46</v>
+      </c>
       <c r="Q118" t="b">
         <v>0</v>
       </c>
@@ -7830,6 +9169,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>51</v>
+      </c>
       <c r="Q119" t="b">
         <v>0</v>
       </c>
@@ -7892,6 +9244,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>32</v>
+      </c>
       <c r="Q120" t="b">
         <v>0</v>
       </c>
@@ -7954,6 +9319,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>51</v>
+      </c>
       <c r="Q121" t="b">
         <v>0</v>
       </c>
@@ -8016,6 +9394,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>54</v>
+      </c>
       <c r="Q122" t="b">
         <v>0</v>
       </c>
@@ -8078,6 +9469,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>50</v>
+      </c>
       <c r="Q123" t="b">
         <v>0</v>
       </c>
@@ -8141,7 +9545,7 @@
         </is>
       </c>
       <c r="Q124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>45</v>
@@ -8202,6 +9606,19 @@
           <t>GSB</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>62</v>
+      </c>
       <c r="Q125" t="b">
         <v>0</v>
       </c>
@@ -8264,6 +9681,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>50</v>
+      </c>
       <c r="Q126" t="b">
         <v>0</v>
       </c>
@@ -8326,6 +9756,19 @@
           <t>GFP</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>48</v>
+      </c>
       <c r="Q127" t="b">
         <v>0</v>
       </c>
@@ -8388,6 +9831,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>31</v>
+      </c>
       <c r="Q128" t="b">
         <v>0</v>
       </c>
@@ -8450,6 +9906,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>55</v>
+      </c>
       <c r="Q129" t="b">
         <v>0</v>
       </c>
@@ -8512,6 +9981,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>47</v>
+      </c>
       <c r="Q130" t="b">
         <v>0</v>
       </c>
@@ -8574,6 +10056,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>49</v>
+      </c>
       <c r="Q131" t="b">
         <v>0</v>
       </c>
@@ -8636,6 +10131,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>41</v>
+      </c>
       <c r="Q132" t="b">
         <v>0</v>
       </c>
@@ -8699,7 +10207,7 @@
         </is>
       </c>
       <c r="Q133" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
         <v>45</v>
@@ -8760,6 +10268,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>50</v>
+      </c>
       <c r="Q134" t="b">
         <v>0</v>
       </c>
@@ -8822,8 +10343,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>40</v>
+      </c>
       <c r="Q135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>45</v>
@@ -8884,6 +10418,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>48</v>
+      </c>
       <c r="Q136" t="b">
         <v>1</v>
       </c>
@@ -8946,8 +10493,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>46</v>
+      </c>
       <c r="Q137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
         <v>45</v>
@@ -9008,6 +10568,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>26</v>
+      </c>
       <c r="Q138" t="b">
         <v>0</v>
       </c>
@@ -9070,6 +10643,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>54</v>
+      </c>
       <c r="Q139" t="b">
         <v>0</v>
       </c>
@@ -9133,7 +10719,7 @@
         </is>
       </c>
       <c r="Q140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
         <v>45</v>
@@ -9194,6 +10780,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>48</v>
+      </c>
       <c r="Q141" t="b">
         <v>0</v>
       </c>
@@ -9256,6 +10855,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>41</v>
+      </c>
       <c r="Q142" t="b">
         <v>0</v>
       </c>
@@ -9318,6 +10930,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>39</v>
+      </c>
       <c r="Q143" t="b">
         <v>0</v>
       </c>
@@ -9380,6 +11005,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>44</v>
+      </c>
       <c r="Q144" t="b">
         <v>0</v>
       </c>
@@ -9442,8 +11080,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>49</v>
+      </c>
       <c r="Q145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
         <v>45</v>
@@ -9504,6 +11155,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>49</v>
+      </c>
       <c r="Q146" t="b">
         <v>0</v>
       </c>
@@ -9566,6 +11230,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>48</v>
+      </c>
       <c r="Q147" t="b">
         <v>0</v>
       </c>
@@ -9628,6 +11305,19 @@
           <t>JMBP</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>59</v>
+      </c>
       <c r="Q148" t="b">
         <v>0</v>
       </c>
@@ -9690,6 +11380,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>48</v>
+      </c>
       <c r="Q149" t="b">
         <v>0</v>
       </c>
@@ -9752,6 +11455,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>49</v>
+      </c>
       <c r="Q150" t="b">
         <v>0</v>
       </c>
@@ -9814,6 +11530,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>29</v>
+      </c>
       <c r="Q151" t="b">
         <v>0</v>
       </c>
@@ -9876,6 +11605,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>52</v>
+      </c>
       <c r="Q152" t="b">
         <v>0</v>
       </c>
@@ -9938,6 +11680,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>58</v>
+      </c>
       <c r="Q153" t="b">
         <v>0</v>
       </c>
@@ -10001,7 +11756,7 @@
         </is>
       </c>
       <c r="Q154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R154" t="n">
         <v>45</v>
@@ -10062,6 +11817,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>45</v>
+      </c>
       <c r="Q155" t="b">
         <v>0</v>
       </c>
@@ -10124,6 +11892,19 @@
           <t>JMBP</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>47</v>
+      </c>
       <c r="Q156" t="b">
         <v>0</v>
       </c>
@@ -10186,6 +11967,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>50</v>
+      </c>
       <c r="Q157" t="b">
         <v>0</v>
       </c>
@@ -10248,6 +12042,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>37</v>
+      </c>
       <c r="Q158" t="b">
         <v>0</v>
       </c>
@@ -10310,6 +12117,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>63</v>
+      </c>
       <c r="Q159" t="b">
         <v>0</v>
       </c>
@@ -10372,6 +12192,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>43</v>
+      </c>
       <c r="Q160" t="b">
         <v>0</v>
       </c>
@@ -10435,7 +12268,7 @@
         </is>
       </c>
       <c r="Q161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
         <v>45</v>
@@ -10496,6 +12329,19 @@
           <t>JMBP</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>50</v>
+      </c>
       <c r="Q162" t="b">
         <v>0</v>
       </c>
@@ -10558,6 +12404,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>43</v>
+      </c>
       <c r="Q163" t="b">
         <v>0</v>
       </c>
@@ -10620,6 +12479,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>53</v>
+      </c>
       <c r="Q164" t="b">
         <v>0</v>
       </c>
@@ -10682,6 +12554,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>52</v>
+      </c>
       <c r="Q165" t="b">
         <v>0</v>
       </c>
@@ -10744,6 +12629,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>50</v>
+      </c>
       <c r="Q166" t="b">
         <v>0</v>
       </c>
@@ -10806,8 +12704,21 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>63</v>
+      </c>
       <c r="Q167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
         <v>45</v>
@@ -10868,6 +12779,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>53</v>
+      </c>
       <c r="Q168" t="b">
         <v>0</v>
       </c>
@@ -10930,6 +12854,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>34</v>
+      </c>
       <c r="Q169" t="b">
         <v>0</v>
       </c>
@@ -10992,6 +12929,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>46</v>
+      </c>
       <c r="Q170" t="b">
         <v>0</v>
       </c>
@@ -11054,6 +13004,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>54</v>
+      </c>
       <c r="Q171" t="b">
         <v>0</v>
       </c>
@@ -11117,7 +13080,7 @@
         </is>
       </c>
       <c r="Q172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
         <v>45</v>
@@ -11178,6 +13141,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>36</v>
+      </c>
       <c r="Q173" t="b">
         <v>0</v>
       </c>
@@ -11240,6 +13216,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>63</v>
+      </c>
       <c r="Q174" t="b">
         <v>0</v>
       </c>
@@ -11302,6 +13291,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>75</v>
+      </c>
       <c r="Q175" t="b">
         <v>0</v>
       </c>
@@ -11364,6 +13366,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>38</v>
+      </c>
       <c r="Q176" t="b">
         <v>0</v>
       </c>
@@ -11426,6 +13441,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>48</v>
+      </c>
       <c r="Q177" t="b">
         <v>0</v>
       </c>
@@ -11488,6 +13516,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>28</v>
+      </c>
       <c r="Q178" t="b">
         <v>0</v>
       </c>
@@ -11550,6 +13591,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>60</v>
+      </c>
       <c r="Q179" t="b">
         <v>0</v>
       </c>
@@ -11612,6 +13666,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>37</v>
+      </c>
       <c r="Q180" t="b">
         <v>0</v>
       </c>
@@ -11675,7 +13742,7 @@
         </is>
       </c>
       <c r="Q181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
         <v>45</v>
@@ -11736,6 +13803,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>46</v>
+      </c>
       <c r="Q182" t="b">
         <v>0</v>
       </c>
@@ -11798,6 +13878,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>70</v>
+      </c>
       <c r="Q183" t="b">
         <v>0</v>
       </c>
@@ -11860,6 +13953,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>63</v>
+      </c>
       <c r="Q184" t="b">
         <v>0</v>
       </c>
@@ -11922,6 +14028,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>40</v>
+      </c>
       <c r="Q185" t="b">
         <v>0</v>
       </c>
@@ -11984,6 +14103,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>38</v>
+      </c>
       <c r="Q186" t="b">
         <v>0</v>
       </c>
@@ -12046,6 +14178,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>47</v>
+      </c>
       <c r="Q187" t="b">
         <v>0</v>
       </c>
@@ -12108,6 +14253,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>66</v>
+      </c>
       <c r="Q188" t="b">
         <v>0</v>
       </c>
@@ -12171,7 +14329,7 @@
         </is>
       </c>
       <c r="Q189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
         <v>45</v>
@@ -12232,6 +14390,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>30</v>
+      </c>
       <c r="Q190" t="b">
         <v>0</v>
       </c>
@@ -12294,6 +14465,19 @@
           <t>SBBGP</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>61</v>
+      </c>
       <c r="Q191" t="b">
         <v>0</v>
       </c>
@@ -12356,6 +14540,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>65</v>
+      </c>
       <c r="Q192" t="b">
         <v>1</v>
       </c>
@@ -12418,6 +14615,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>51</v>
+      </c>
       <c r="Q193" t="b">
         <v>0</v>
       </c>
@@ -12480,6 +14690,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>53</v>
+      </c>
       <c r="Q194" t="b">
         <v>0</v>
       </c>
@@ -12542,6 +14765,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>65</v>
+      </c>
       <c r="Q195" t="b">
         <v>0</v>
       </c>
@@ -12604,6 +14840,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>47</v>
+      </c>
       <c r="Q196" t="b">
         <v>0</v>
       </c>
@@ -12667,7 +14916,7 @@
         </is>
       </c>
       <c r="Q197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
         <v>45</v>
@@ -12728,6 +14977,19 @@
           <t>GSB</t>
         </is>
       </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>29</v>
+      </c>
       <c r="Q198" t="b">
         <v>0</v>
       </c>
@@ -12790,6 +15052,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>57</v>
+      </c>
       <c r="Q199" t="b">
         <v>0</v>
       </c>
@@ -12852,6 +15127,19 @@
           <t>JMBP</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>51</v>
+      </c>
       <c r="Q200" t="b">
         <v>0</v>
       </c>
@@ -12914,8 +15202,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>46</v>
+      </c>
       <c r="Q201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R201" t="n">
         <v>45</v>
@@ -12976,6 +15277,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>58</v>
+      </c>
       <c r="Q202" t="b">
         <v>1</v>
       </c>
@@ -13038,6 +15352,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P203" t="n">
+        <v>40</v>
+      </c>
       <c r="Q203" t="b">
         <v>0</v>
       </c>
@@ -13100,6 +15427,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>40</v>
+      </c>
       <c r="Q204" t="b">
         <v>0</v>
       </c>
@@ -13162,6 +15502,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>41</v>
+      </c>
       <c r="Q205" t="b">
         <v>0</v>
       </c>
@@ -13225,7 +15578,7 @@
         </is>
       </c>
       <c r="Q206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
         <v>45</v>
@@ -13286,6 +15639,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>38</v>
+      </c>
       <c r="Q207" t="b">
         <v>0</v>
       </c>
@@ -13348,6 +15714,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>64</v>
+      </c>
       <c r="Q208" t="b">
         <v>0</v>
       </c>
@@ -13410,6 +15789,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>45</v>
+      </c>
       <c r="Q209" t="b">
         <v>0</v>
       </c>
@@ -13472,6 +15864,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>52</v>
+      </c>
       <c r="Q210" t="b">
         <v>0</v>
       </c>
@@ -13534,6 +15939,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>58</v>
+      </c>
       <c r="Q211" t="b">
         <v>0</v>
       </c>
@@ -13596,6 +16014,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>51</v>
+      </c>
       <c r="Q212" t="b">
         <v>0</v>
       </c>
@@ -13658,6 +16089,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>61</v>
+      </c>
       <c r="Q213" t="b">
         <v>0</v>
       </c>
@@ -13720,6 +16164,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>38</v>
+      </c>
       <c r="Q214" t="b">
         <v>0</v>
       </c>
@@ -13783,7 +16240,7 @@
         </is>
       </c>
       <c r="Q215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
         <v>45</v>
@@ -13844,6 +16301,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>39</v>
+      </c>
       <c r="Q216" t="b">
         <v>0</v>
       </c>
@@ -13906,6 +16376,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P217" t="n">
+        <v>54</v>
+      </c>
       <c r="Q217" t="b">
         <v>0</v>
       </c>
@@ -13968,6 +16451,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>62</v>
+      </c>
       <c r="Q218" t="b">
         <v>0</v>
       </c>
@@ -14030,6 +16526,19 @@
           <t>JMBP</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>47</v>
+      </c>
       <c r="Q219" t="b">
         <v>0</v>
       </c>
@@ -14092,6 +16601,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>62</v>
+      </c>
       <c r="Q220" t="b">
         <v>1</v>
       </c>
@@ -14154,6 +16676,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>52</v>
+      </c>
       <c r="Q221" t="b">
         <v>0</v>
       </c>
@@ -14216,6 +16751,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>45</v>
+      </c>
       <c r="Q222" t="b">
         <v>0</v>
       </c>
@@ -14278,6 +16826,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>37</v>
+      </c>
       <c r="Q223" t="b">
         <v>0</v>
       </c>
@@ -14340,6 +16901,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>65</v>
+      </c>
       <c r="Q224" t="b">
         <v>0</v>
       </c>
@@ -14403,7 +16977,7 @@
         </is>
       </c>
       <c r="Q225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R225" t="n">
         <v>45</v>
@@ -14464,6 +17038,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>35</v>
+      </c>
       <c r="Q226" t="b">
         <v>0</v>
       </c>
@@ -14526,8 +17113,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>66</v>
+      </c>
       <c r="Q227" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R227" t="n">
         <v>45</v>
@@ -14588,8 +17188,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>57</v>
+      </c>
       <c r="Q228" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R228" t="n">
         <v>45</v>
@@ -14650,6 +17263,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>35</v>
+      </c>
       <c r="Q229" t="b">
         <v>0</v>
       </c>
@@ -14712,6 +17338,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>43</v>
+      </c>
       <c r="Q230" t="b">
         <v>0</v>
       </c>
@@ -14774,6 +17413,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>43</v>
+      </c>
       <c r="Q231" t="b">
         <v>0</v>
       </c>
@@ -14836,6 +17488,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>57</v>
+      </c>
       <c r="Q232" t="b">
         <v>0</v>
       </c>
@@ -14898,6 +17563,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>51</v>
+      </c>
       <c r="Q233" t="b">
         <v>0</v>
       </c>
@@ -14960,6 +17638,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>69</v>
+      </c>
       <c r="Q234" t="b">
         <v>0</v>
       </c>
@@ -15023,7 +17714,7 @@
         </is>
       </c>
       <c r="Q235" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R235" t="n">
         <v>45</v>
@@ -15084,6 +17775,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>31</v>
+      </c>
       <c r="Q236" t="b">
         <v>0</v>
       </c>
@@ -15146,6 +17850,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>49</v>
+      </c>
       <c r="Q237" t="b">
         <v>0</v>
       </c>
@@ -15208,6 +17925,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P238" t="n">
+        <v>64</v>
+      </c>
       <c r="Q238" t="b">
         <v>0</v>
       </c>
@@ -15270,6 +18000,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>43</v>
+      </c>
       <c r="Q239" t="b">
         <v>0</v>
       </c>
@@ -15332,6 +18075,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P240" t="n">
+        <v>54</v>
+      </c>
       <c r="Q240" t="b">
         <v>0</v>
       </c>
@@ -15394,6 +18150,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>57</v>
+      </c>
       <c r="Q241" t="b">
         <v>0</v>
       </c>
@@ -15456,6 +18225,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P242" t="n">
+        <v>45</v>
+      </c>
       <c r="Q242" t="b">
         <v>0</v>
       </c>
@@ -15518,8 +18300,21 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P243" t="n">
+        <v>67</v>
+      </c>
       <c r="Q243" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R243" t="n">
         <v>45</v>
@@ -15580,6 +18375,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P244" t="n">
+        <v>63</v>
+      </c>
       <c r="Q244" t="b">
         <v>0</v>
       </c>
@@ -15643,7 +18451,7 @@
         </is>
       </c>
       <c r="Q245" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R245" t="n">
         <v>45</v>
@@ -15704,6 +18512,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P246" t="n">
+        <v>52</v>
+      </c>
       <c r="Q246" t="b">
         <v>0</v>
       </c>
@@ -15766,6 +18587,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P247" t="n">
+        <v>54</v>
+      </c>
       <c r="Q247" t="b">
         <v>0</v>
       </c>
@@ -15828,6 +18662,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P248" t="n">
+        <v>37</v>
+      </c>
       <c r="Q248" t="b">
         <v>0</v>
       </c>
@@ -15890,6 +18737,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P249" t="n">
+        <v>55</v>
+      </c>
       <c r="Q249" t="b">
         <v>0</v>
       </c>
@@ -15952,6 +18812,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P250" t="n">
+        <v>45</v>
+      </c>
       <c r="Q250" t="b">
         <v>0</v>
       </c>
@@ -16014,6 +18887,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P251" t="n">
+        <v>42</v>
+      </c>
       <c r="Q251" t="b">
         <v>0</v>
       </c>
@@ -16077,7 +18963,7 @@
         </is>
       </c>
       <c r="Q252" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R252" t="n">
         <v>45</v>
@@ -16138,6 +19024,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P253" t="n">
+        <v>54</v>
+      </c>
       <c r="Q253" t="b">
         <v>0</v>
       </c>
@@ -16200,6 +19099,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P254" t="n">
+        <v>55</v>
+      </c>
       <c r="Q254" t="b">
         <v>0</v>
       </c>
@@ -16262,6 +19174,19 @@
           <t>GFP</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P255" t="n">
+        <v>51</v>
+      </c>
       <c r="Q255" t="b">
         <v>1</v>
       </c>
@@ -16324,8 +19249,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P256" t="n">
+        <v>50</v>
+      </c>
       <c r="Q256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
         <v>45</v>
@@ -16386,6 +19324,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P257" t="n">
+        <v>30</v>
+      </c>
       <c r="Q257" t="b">
         <v>0</v>
       </c>
@@ -16448,6 +19399,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P258" t="n">
+        <v>46</v>
+      </c>
       <c r="Q258" t="b">
         <v>0</v>
       </c>
@@ -16510,6 +19474,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P259" t="n">
+        <v>33</v>
+      </c>
       <c r="Q259" t="b">
         <v>0</v>
       </c>
@@ -16573,7 +19550,7 @@
         </is>
       </c>
       <c r="Q260" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R260" t="n">
         <v>45</v>
@@ -16634,6 +19611,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>51</v>
+      </c>
       <c r="Q261" t="b">
         <v>0</v>
       </c>
@@ -16696,6 +19686,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>67</v>
+      </c>
       <c r="Q262" t="b">
         <v>1</v>
       </c>
@@ -16758,6 +19761,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P263" t="n">
+        <v>67</v>
+      </c>
       <c r="Q263" t="b">
         <v>0</v>
       </c>
@@ -16820,6 +19836,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>46</v>
+      </c>
       <c r="Q264" t="b">
         <v>0</v>
       </c>
@@ -16882,6 +19911,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P265" t="n">
+        <v>52</v>
+      </c>
       <c r="Q265" t="b">
         <v>0</v>
       </c>
@@ -16944,6 +19986,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>59</v>
+      </c>
       <c r="Q266" t="b">
         <v>0</v>
       </c>
@@ -17007,7 +20062,7 @@
         </is>
       </c>
       <c r="Q267" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R267" t="n">
         <v>45</v>
@@ -17068,6 +20123,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>44</v>
+      </c>
       <c r="Q268" t="b">
         <v>0</v>
       </c>
@@ -17130,6 +20198,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>72</v>
+      </c>
       <c r="Q269" t="b">
         <v>0</v>
       </c>
@@ -17192,6 +20273,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P270" t="n">
+        <v>51</v>
+      </c>
       <c r="Q270" t="b">
         <v>0</v>
       </c>
@@ -17254,6 +20348,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P271" t="n">
+        <v>38</v>
+      </c>
       <c r="Q271" t="b">
         <v>0</v>
       </c>
@@ -17316,6 +20423,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>44</v>
+      </c>
       <c r="Q272" t="b">
         <v>0</v>
       </c>
@@ -17379,7 +20499,7 @@
         </is>
       </c>
       <c r="Q273" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R273" t="n">
         <v>45</v>
@@ -17440,6 +20560,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P274" t="n">
+        <v>58</v>
+      </c>
       <c r="Q274" t="b">
         <v>0</v>
       </c>
@@ -17502,6 +20635,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P275" t="n">
+        <v>41</v>
+      </c>
       <c r="Q275" t="b">
         <v>0</v>
       </c>
@@ -17564,6 +20710,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P276" t="n">
+        <v>55</v>
+      </c>
       <c r="Q276" t="b">
         <v>0</v>
       </c>
@@ -17626,6 +20785,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>26</v>
+      </c>
       <c r="Q277" t="b">
         <v>0</v>
       </c>
@@ -17688,6 +20860,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P278" t="n">
+        <v>43</v>
+      </c>
       <c r="Q278" t="b">
         <v>0</v>
       </c>
@@ -17750,6 +20935,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P279" t="n">
+        <v>56</v>
+      </c>
       <c r="Q279" t="b">
         <v>0</v>
       </c>
@@ -17812,6 +21010,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P280" t="n">
+        <v>35</v>
+      </c>
       <c r="Q280" t="b">
         <v>0</v>
       </c>
@@ -17875,7 +21086,7 @@
         </is>
       </c>
       <c r="Q281" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R281" t="n">
         <v>45</v>
@@ -17936,6 +21147,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>55</v>
+      </c>
       <c r="Q282" t="b">
         <v>0</v>
       </c>
@@ -17998,6 +21222,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P283" t="n">
+        <v>47</v>
+      </c>
       <c r="Q283" t="b">
         <v>0</v>
       </c>
@@ -18060,6 +21297,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P284" t="n">
+        <v>37</v>
+      </c>
       <c r="Q284" t="b">
         <v>0</v>
       </c>
@@ -18122,6 +21372,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P285" t="n">
+        <v>51</v>
+      </c>
       <c r="Q285" t="b">
         <v>0</v>
       </c>
@@ -18184,6 +21447,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P286" t="n">
+        <v>51</v>
+      </c>
       <c r="Q286" t="b">
         <v>0</v>
       </c>
@@ -18246,6 +21522,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P287" t="n">
+        <v>58</v>
+      </c>
       <c r="Q287" t="b">
         <v>0</v>
       </c>
@@ -18308,6 +21597,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>60</v>
+      </c>
       <c r="Q288" t="b">
         <v>0</v>
       </c>
@@ -18370,6 +21672,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>50</v>
+      </c>
       <c r="Q289" t="b">
         <v>0</v>
       </c>
@@ -18432,6 +21747,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P290" t="n">
+        <v>48</v>
+      </c>
       <c r="Q290" t="b">
         <v>0</v>
       </c>
@@ -18495,7 +21823,7 @@
         </is>
       </c>
       <c r="Q291" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R291" t="n">
         <v>45</v>
@@ -18556,6 +21884,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P292" t="n">
+        <v>60</v>
+      </c>
       <c r="Q292" t="b">
         <v>0</v>
       </c>
@@ -18618,8 +21959,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P293" t="n">
+        <v>53</v>
+      </c>
       <c r="Q293" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R293" t="n">
         <v>45</v>
@@ -18680,6 +22034,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>50</v>
+      </c>
       <c r="Q294" t="b">
         <v>0</v>
       </c>
@@ -18742,8 +22109,21 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P295" t="n">
+        <v>52</v>
+      </c>
       <c r="Q295" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R295" t="n">
         <v>45</v>
@@ -18804,6 +22184,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P296" t="n">
+        <v>46</v>
+      </c>
       <c r="Q296" t="b">
         <v>0</v>
       </c>
@@ -18866,6 +22259,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P297" t="n">
+        <v>55</v>
+      </c>
       <c r="Q297" t="b">
         <v>0</v>
       </c>
@@ -18928,6 +22334,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P298" t="n">
+        <v>43</v>
+      </c>
       <c r="Q298" t="b">
         <v>0</v>
       </c>
@@ -18990,6 +22409,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P299" t="n">
+        <v>59</v>
+      </c>
       <c r="Q299" t="b">
         <v>0</v>
       </c>
@@ -19052,6 +22484,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P300" t="n">
+        <v>45</v>
+      </c>
       <c r="Q300" t="b">
         <v>0</v>
       </c>
@@ -19115,7 +22560,7 @@
         </is>
       </c>
       <c r="Q301" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R301" t="n">
         <v>45</v>
@@ -19176,6 +22621,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P302" t="n">
+        <v>46</v>
+      </c>
       <c r="Q302" t="b">
         <v>0</v>
       </c>
@@ -19238,6 +22696,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P303" t="n">
+        <v>50</v>
+      </c>
       <c r="Q303" t="b">
         <v>0</v>
       </c>
@@ -19300,6 +22771,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P304" t="n">
+        <v>42</v>
+      </c>
       <c r="Q304" t="b">
         <v>0</v>
       </c>
@@ -19362,6 +22846,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P305" t="n">
+        <v>65</v>
+      </c>
       <c r="Q305" t="b">
         <v>0</v>
       </c>
@@ -19425,7 +22922,7 @@
         </is>
       </c>
       <c r="Q306" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R306" t="n">
         <v>45</v>
@@ -19486,6 +22983,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>43</v>
+      </c>
       <c r="Q307" t="b">
         <v>0</v>
       </c>
@@ -19548,6 +23058,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
+        <v>65</v>
+      </c>
       <c r="Q308" t="b">
         <v>0</v>
       </c>
@@ -19610,6 +23133,19 @@
           <t>SHS</t>
         </is>
       </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>47</v>
+      </c>
       <c r="Q309" t="b">
         <v>0</v>
       </c>
@@ -19672,6 +23208,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P310" t="n">
+        <v>49</v>
+      </c>
       <c r="Q310" t="b">
         <v>1</v>
       </c>
@@ -19734,6 +23283,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P311" t="n">
+        <v>38</v>
+      </c>
       <c r="Q311" t="b">
         <v>0</v>
       </c>
@@ -19796,6 +23358,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>39</v>
+      </c>
       <c r="Q312" t="b">
         <v>0</v>
       </c>
@@ -19858,6 +23433,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>50</v>
+      </c>
       <c r="Q313" t="b">
         <v>0</v>
       </c>
@@ -19920,6 +23508,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P314" t="n">
+        <v>53</v>
+      </c>
       <c r="Q314" t="b">
         <v>0</v>
       </c>
@@ -19983,7 +23584,7 @@
         </is>
       </c>
       <c r="Q315" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R315" t="n">
         <v>45</v>
@@ -20044,6 +23645,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P316" t="n">
+        <v>40</v>
+      </c>
       <c r="Q316" t="b">
         <v>0</v>
       </c>
@@ -20106,8 +23720,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P317" t="n">
+        <v>63</v>
+      </c>
       <c r="Q317" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R317" t="n">
         <v>45</v>
@@ -20168,6 +23795,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P318" t="n">
+        <v>49</v>
+      </c>
       <c r="Q318" t="b">
         <v>0</v>
       </c>
@@ -20230,6 +23870,19 @@
           <t>MAG</t>
         </is>
       </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P319" t="n">
+        <v>45</v>
+      </c>
       <c r="Q319" t="b">
         <v>0</v>
       </c>
@@ -20292,6 +23945,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P320" t="n">
+        <v>27</v>
+      </c>
       <c r="Q320" t="b">
         <v>0</v>
       </c>
@@ -20354,6 +24020,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>51</v>
+      </c>
       <c r="Q321" t="b">
         <v>0</v>
       </c>
@@ -20416,6 +24095,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P322" t="n">
+        <v>41</v>
+      </c>
       <c r="Q322" t="b">
         <v>0</v>
       </c>
@@ -20478,6 +24170,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P323" t="n">
+        <v>48</v>
+      </c>
       <c r="Q323" t="b">
         <v>0</v>
       </c>
@@ -20541,7 +24246,7 @@
         </is>
       </c>
       <c r="Q324" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R324" t="n">
         <v>45</v>
@@ -20602,6 +24307,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P325" t="n">
+        <v>55</v>
+      </c>
       <c r="Q325" t="b">
         <v>0</v>
       </c>
@@ -20664,6 +24382,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>42</v>
+      </c>
       <c r="Q326" t="b">
         <v>0</v>
       </c>
@@ -20726,6 +24457,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P327" t="n">
+        <v>45</v>
+      </c>
       <c r="Q327" t="b">
         <v>0</v>
       </c>
@@ -20788,6 +24532,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P328" t="n">
+        <v>28</v>
+      </c>
       <c r="Q328" t="b">
         <v>0</v>
       </c>
@@ -20850,6 +24607,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P329" t="n">
+        <v>41</v>
+      </c>
       <c r="Q329" t="b">
         <v>0</v>
       </c>
@@ -20913,7 +24683,7 @@
         </is>
       </c>
       <c r="Q330" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R330" t="n">
         <v>45</v>
@@ -20974,6 +24744,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P331" t="n">
+        <v>37</v>
+      </c>
       <c r="Q331" t="b">
         <v>0</v>
       </c>
@@ -21036,6 +24819,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P332" t="n">
+        <v>42</v>
+      </c>
       <c r="Q332" t="b">
         <v>0</v>
       </c>
@@ -21098,6 +24894,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P333" t="n">
+        <v>60</v>
+      </c>
       <c r="Q333" t="b">
         <v>0</v>
       </c>
@@ -21160,6 +24969,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P334" t="n">
+        <v>53</v>
+      </c>
       <c r="Q334" t="b">
         <v>0</v>
       </c>
@@ -21222,6 +25044,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P335" t="n">
+        <v>70</v>
+      </c>
       <c r="Q335" t="b">
         <v>0</v>
       </c>
@@ -21284,6 +25119,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P336" t="n">
+        <v>47</v>
+      </c>
       <c r="Q336" t="b">
         <v>0</v>
       </c>
@@ -21346,6 +25194,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P337" t="n">
+        <v>60</v>
+      </c>
       <c r="Q337" t="b">
         <v>0</v>
       </c>
@@ -21408,6 +25269,19 @@
           <t>RVLTGONP</t>
         </is>
       </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P338" t="n">
+        <v>48</v>
+      </c>
       <c r="Q338" t="b">
         <v>0</v>
       </c>
@@ -21470,6 +25344,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P339" t="n">
+        <v>45</v>
+      </c>
       <c r="Q339" t="b">
         <v>0</v>
       </c>
@@ -21532,6 +25419,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P340" t="n">
+        <v>35</v>
+      </c>
       <c r="Q340" t="b">
         <v>0</v>
       </c>
@@ -21595,7 +25495,7 @@
         </is>
       </c>
       <c r="Q341" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R341" t="n">
         <v>45</v>
@@ -21655,6 +25555,19 @@
         <is>
           <t>IND</t>
         </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P342" t="n">
+        <v>38</v>
       </c>
       <c r="Q342" t="b">
         <v>0</v>
